--- a/output/pdf_financials_xlsx/LAB.xlsx
+++ b/output/pdf_financials_xlsx/LAB.xlsx
@@ -5907,40 +5907,40 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.231512</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.267616</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.267616</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.274968</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.358212</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.74851</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.101865</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.713305</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.419099</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.597023</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.705377</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.850377</v>
       </c>
     </row>
     <row r="93">
@@ -9538,7 +9538,11 @@
           <t>Share-based payments reserve (note 6)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -11450,7 +11454,11 @@
           <t>Share-based payments reserve 4</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LAB.xlsx
+++ b/output/pdf_financials_xlsx/LAB.xlsx
@@ -2465,28 +2465,28 @@
         <v>0.106339</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.033907</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.135739</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003745</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.010019</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.140959</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.982715</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.403466</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>33.245743</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>21.354986</v>
@@ -2579,28 +2579,28 @@
         <v>0.106339</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.033907</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.135739</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003745</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.010019</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.140959</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.982715</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.403466</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>33.245743</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>21.354986</v>
@@ -3263,28 +3263,28 @@
         <v>0.0001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.034007</v>
+        <v>0.0001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.135739</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.003745</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.010019</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.141457</v>
+        <v>0.000498</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.984437</v>
+        <v>0.001722</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.415152</v>
+        <v>0.011686</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>33.315437</v>
+        <v>0.06969400000000001</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.08581800000000001</v>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
